--- a/Result/checksunmy.xlsx
+++ b/Result/checksunmy.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7357,7 +7437,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7645,7 +7729,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -7933,7 +8021,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8221,7 +8313,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8509,7 +8605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -8797,7 +8897,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9085,7 +9189,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9373,7 +9481,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9661,7 +9773,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -9949,7 +10065,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -10529,7 +10649,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -10817,7 +10941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -11105,7 +11233,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -11393,7 +11525,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11681,7 +11817,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -11969,7 +12109,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -12257,7 +12401,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -12545,7 +12693,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -12833,7 +12985,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -13121,7 +13277,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -13701,7 +13861,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -13989,7 +14153,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -14277,7 +14445,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -14565,7 +14737,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -14853,7 +15029,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -15141,7 +15321,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -15429,7 +15613,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -15717,7 +15905,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -16005,7 +16197,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -16293,7 +16489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2025-08-25</t>

--- a/Result/checksunmy.xlsx
+++ b/Result/checksunmy.xlsx
@@ -19178,7 +19178,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -19198,184 +19198,184 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>-4.88</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>-22.55</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>-2</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>1.0</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>-4.88</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
-        <is>
-          <t>-22.55</t>
-        </is>
-      </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>2025-03-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>32.15</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>32.95</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>2025-08-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>2025-08-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD52" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="AE52" t="inlineStr">
+        <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="AF52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG52" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="AH52" t="inlineStr">
+        <is>
+          <t>-1.15</t>
+        </is>
+      </c>
+      <c r="AI52" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="AJ52" t="inlineStr">
+        <is>
+          <t>-3.13</t>
+        </is>
+      </c>
+      <c r="AK52" t="inlineStr">
+        <is>
+          <t>22.66</t>
+        </is>
+      </c>
+      <c r="AL52" t="inlineStr">
+        <is>
+          <t>22.0825</t>
+        </is>
+      </c>
+      <c r="AM52" t="inlineStr">
+        <is>
+          <t>22.797</t>
+        </is>
+      </c>
+      <c r="AN52" t="inlineStr">
+        <is>
+          <t>129.84</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AQ52" t="inlineStr">
+        <is>
+          <t>26.08695652173891</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>36.04700352526435</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr">
+        <is>
+          <t>-6.21</t>
+        </is>
+      </c>
+      <c r="AT52" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="T52" t="inlineStr">
-        <is>
-          <t>-2</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V52" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="W52" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>2025-03-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y52" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
-      </c>
-      <c r="AA52" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>2025-08-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>2025-08-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD52" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="AE52" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AF52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH52" t="inlineStr">
-        <is>
-          <t>-1.15</t>
-        </is>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="AJ52" t="inlineStr">
-        <is>
-          <t>-3.13</t>
-        </is>
-      </c>
-      <c r="AK52" t="inlineStr">
-        <is>
-          <t>22.66</t>
-        </is>
-      </c>
-      <c r="AL52" t="inlineStr">
-        <is>
-          <t>22.0825</t>
-        </is>
-      </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>22.797</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>129.84</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AP52" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AQ52" t="inlineStr">
-        <is>
-          <t>26.08695652173891</t>
-        </is>
-      </c>
-      <c r="AR52" t="inlineStr">
-        <is>
-          <t>36.04700352526435</t>
-        </is>
-      </c>
-      <c r="AS52" t="inlineStr">
-        <is>
-          <t>-6.21</t>
-        </is>
-      </c>
-      <c r="AT52" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU52" t="inlineStr">
         <is>
           <t>7417340.6</t>
@@ -19433,62 +19433,62 @@
       </c>
       <c r="BF52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="BG52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="BI52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BJ52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="BK52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="BL52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="BM52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="BN52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="BO52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="BP52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="BQ52" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BR52" t="inlineStr">
@@ -19503,12 +19503,12 @@
       </c>
       <c r="BT52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BU52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
@@ -19545,7 +19545,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -19565,12 +19565,12 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
@@ -19615,7 +19615,7 @@
       </c>
       <c r="U53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="V53" t="inlineStr">
@@ -19625,7 +19625,7 @@
       </c>
       <c r="W53" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-4.0</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
@@ -19670,12 +19670,12 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AH53" t="inlineStr">
@@ -19800,62 +19800,62 @@
       </c>
       <c r="BF53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="BG53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="BI53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BJ53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="BK53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="BL53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="BM53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="BN53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="BO53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="BP53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="BQ53" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BR53" t="inlineStr">
@@ -19870,12 +19870,12 @@
       </c>
       <c r="BT53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BU53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
@@ -19912,7 +19912,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>3.92</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -19932,12 +19932,12 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
@@ -19982,7 +19982,7 @@
       </c>
       <c r="U54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V54" t="inlineStr">
@@ -19992,7 +19992,7 @@
       </c>
       <c r="W54" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
@@ -20037,12 +20037,12 @@
       </c>
       <c r="AF54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AH54" t="inlineStr">
@@ -20167,62 +20167,62 @@
       </c>
       <c r="BF54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="BG54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="BI54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BJ54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="BK54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="BL54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="BM54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="BN54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="BO54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="BP54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="BQ54" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BR54" t="inlineStr">
@@ -20237,12 +20237,12 @@
       </c>
       <c r="BT54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BU54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
@@ -20279,7 +20279,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -20299,184 +20299,184 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>-2.76</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>-22.55</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O55" t="inlineStr">
-        <is>
-          <t>-2.76</t>
-        </is>
-      </c>
-      <c r="P55" t="inlineStr">
-        <is>
-          <t>-22.55</t>
-        </is>
-      </c>
-      <c r="Q55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R55" t="inlineStr">
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>2025-03-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>32.15</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>32.95</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>2025-08-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>2025-08-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD55" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="AE55" t="inlineStr">
+        <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="AF55" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG55" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="AH55" t="inlineStr">
+        <is>
+          <t>0.39</t>
+        </is>
+      </c>
+      <c r="AI55" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="AJ55" t="inlineStr">
+        <is>
+          <t>-3.85</t>
+        </is>
+      </c>
+      <c r="AK55" t="inlineStr">
+        <is>
+          <t>22.81</t>
+        </is>
+      </c>
+      <c r="AL55" t="inlineStr">
+        <is>
+          <t>22.0575</t>
+        </is>
+      </c>
+      <c r="AM55" t="inlineStr">
+        <is>
+          <t>22.94</t>
+        </is>
+      </c>
+      <c r="AN55" t="inlineStr">
+        <is>
+          <t>117.19</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>0.03</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>-0.20</t>
+        </is>
+      </c>
+      <c r="AQ55" t="inlineStr">
+        <is>
+          <t>81.08108108108102</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>93.69369369369367</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr">
+        <is>
+          <t>12.03</t>
+        </is>
+      </c>
+      <c r="AT55" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S55" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="T55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W55" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>2025-03-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y55" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
-      </c>
-      <c r="AA55" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>2025-08-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>2025-08-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD55" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="AE55" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AF55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH55" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>3.41</t>
-        </is>
-      </c>
-      <c r="AJ55" t="inlineStr">
-        <is>
-          <t>-3.85</t>
-        </is>
-      </c>
-      <c r="AK55" t="inlineStr">
-        <is>
-          <t>22.81</t>
-        </is>
-      </c>
-      <c r="AL55" t="inlineStr">
-        <is>
-          <t>22.0575</t>
-        </is>
-      </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>22.94</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>117.19</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>0.03</t>
-        </is>
-      </c>
-      <c r="AP55" t="inlineStr">
-        <is>
-          <t>-0.20</t>
-        </is>
-      </c>
-      <c r="AQ55" t="inlineStr">
-        <is>
-          <t>81.08108108108102</t>
-        </is>
-      </c>
-      <c r="AR55" t="inlineStr">
-        <is>
-          <t>93.69369369369367</t>
-        </is>
-      </c>
-      <c r="AS55" t="inlineStr">
-        <is>
-          <t>12.03</t>
-        </is>
-      </c>
-      <c r="AT55" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU55" t="inlineStr">
         <is>
           <t>9171021.4</t>
@@ -20534,62 +20534,62 @@
       </c>
       <c r="BF55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="BG55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="BI55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BJ55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="BK55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="BL55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="BM55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="BN55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="BO55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="BP55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="BQ55" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BR55" t="inlineStr">
@@ -20604,12 +20604,12 @@
       </c>
       <c r="BT55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BU55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
@@ -20646,7 +20646,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -20666,12 +20666,12 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -20716,7 +20716,7 @@
       </c>
       <c r="U56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14</t>
         </is>
       </c>
       <c r="V56" t="inlineStr">
@@ -20726,7 +20726,7 @@
       </c>
       <c r="W56" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
@@ -20771,12 +20771,12 @@
       </c>
       <c r="AF56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AH56" t="inlineStr">
@@ -20901,62 +20901,62 @@
       </c>
       <c r="BF56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="BG56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="BI56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="BJ56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="BK56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="BL56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="BM56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="BN56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="BO56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="BP56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="BQ56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BR56" t="inlineStr">
@@ -20971,12 +20971,12 @@
       </c>
       <c r="BT56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BU56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
@@ -21013,7 +21013,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>5.83</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -21033,12 +21033,12 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.23</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
@@ -21083,7 +21083,7 @@
       </c>
       <c r="U57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="V57" t="inlineStr">
@@ -21093,7 +21093,7 @@
       </c>
       <c r="W57" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.0</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
@@ -21138,12 +21138,12 @@
       </c>
       <c r="AF57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AH57" t="inlineStr">
@@ -21263,67 +21263,67 @@
       </c>
       <c r="BE57" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="BG57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="BI57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="BJ57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="BK57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="BL57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="BM57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="BN57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="BO57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="BP57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="BQ57" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BR57" t="inlineStr">
@@ -21338,12 +21338,12 @@
       </c>
       <c r="BT57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BU57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
@@ -21380,7 +21380,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -21400,12 +21400,12 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
@@ -21450,7 +21450,7 @@
       </c>
       <c r="U58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="V58" t="inlineStr">
@@ -21460,7 +21460,7 @@
       </c>
       <c r="W58" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
@@ -21505,12 +21505,12 @@
       </c>
       <c r="AF58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AH58" t="inlineStr">
@@ -21635,62 +21635,62 @@
       </c>
       <c r="BF58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="BG58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="BI58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BJ58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="BK58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="BL58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="BM58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="BN58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="BO58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="BP58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="BQ58" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BR58" t="inlineStr">
@@ -21705,12 +21705,12 @@
       </c>
       <c r="BT58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BU58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
@@ -21747,7 +21747,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>4.13</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -21767,12 +21767,12 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
@@ -21817,7 +21817,7 @@
       </c>
       <c r="U59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11</t>
         </is>
       </c>
       <c r="V59" t="inlineStr">
@@ -21827,7 +21827,7 @@
       </c>
       <c r="W59" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>11.0</t>
         </is>
       </c>
       <c r="X59" t="inlineStr">
@@ -21872,12 +21872,12 @@
       </c>
       <c r="AF59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AH59" t="inlineStr">
@@ -21997,67 +21997,67 @@
       </c>
       <c r="BE59" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BF59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="BG59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="BI59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="BJ59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="BK59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="BL59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="BM59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="BN59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="BO59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="BP59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="BQ59" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BR59" t="inlineStr">
@@ -22072,12 +22072,12 @@
       </c>
       <c r="BT59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BU59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
@@ -22114,7 +22114,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -22134,184 +22134,184 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
+          <t>-1.08</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>-6.16</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>-22.55</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>-65.0</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>-6.16</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
-        <is>
-          <t>-22.55</t>
-        </is>
-      </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>2025-03-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-03-10 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>32.15</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>32.95</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>2025-08-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>2025-08-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD60" t="inlineStr">
+        <is>
+          <t>24.9</t>
+        </is>
+      </c>
+      <c r="AE60" t="inlineStr">
+        <is>
+          <t>23.55</t>
+        </is>
+      </c>
+      <c r="AF60" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG60" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="AH60" t="inlineStr">
+        <is>
+          <t>2.03</t>
+        </is>
+      </c>
+      <c r="AI60" t="inlineStr">
+        <is>
+          <t>-1.17</t>
+        </is>
+      </c>
+      <c r="AJ60" t="inlineStr">
+        <is>
+          <t>-5.36</t>
+        </is>
+      </c>
+      <c r="AK60" t="inlineStr">
+        <is>
+          <t>21.66</t>
+        </is>
+      </c>
+      <c r="AL60" t="inlineStr">
+        <is>
+          <t>21.9175</t>
+        </is>
+      </c>
+      <c r="AM60" t="inlineStr">
+        <is>
+          <t>23.159</t>
+        </is>
+      </c>
+      <c r="AN60" t="inlineStr">
+        <is>
+          <t>22.01</t>
+        </is>
+      </c>
+      <c r="AO60" t="inlineStr">
+        <is>
+          <t>-0.35</t>
+        </is>
+      </c>
+      <c r="AP60" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="AQ60" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AR60" t="inlineStr">
+        <is>
+          <t>60.7843137254901</t>
+        </is>
+      </c>
+      <c r="AS60" t="inlineStr">
+        <is>
+          <t>-5.07</t>
+        </is>
+      </c>
+      <c r="AT60" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
-        <is>
-          <t>-65.0</t>
-        </is>
-      </c>
-      <c r="T60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="V60" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="W60" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>2025-03-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y60" t="inlineStr">
-        <is>
-          <t>2025-03-10 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
-      </c>
-      <c r="AA60" t="inlineStr">
-        <is>
-          <t>32.95</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>2025-08-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>2025-08-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD60" t="inlineStr">
-        <is>
-          <t>24.9</t>
-        </is>
-      </c>
-      <c r="AE60" t="inlineStr">
-        <is>
-          <t>23.55</t>
-        </is>
-      </c>
-      <c r="AF60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH60" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>-1.17</t>
-        </is>
-      </c>
-      <c r="AJ60" t="inlineStr">
-        <is>
-          <t>-5.36</t>
-        </is>
-      </c>
-      <c r="AK60" t="inlineStr">
-        <is>
-          <t>21.66</t>
-        </is>
-      </c>
-      <c r="AL60" t="inlineStr">
-        <is>
-          <t>21.9175</t>
-        </is>
-      </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>23.159</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>22.01</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>-0.35</t>
-        </is>
-      </c>
-      <c r="AP60" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="AQ60" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AR60" t="inlineStr">
-        <is>
-          <t>60.7843137254901</t>
-        </is>
-      </c>
-      <c r="AS60" t="inlineStr">
-        <is>
-          <t>-5.07</t>
-        </is>
-      </c>
-      <c r="AT60" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
       <c r="AU60" t="inlineStr">
         <is>
           <t>7201148.0</t>
@@ -22369,62 +22369,62 @@
       </c>
       <c r="BF60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="BG60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="BI60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.62</t>
         </is>
       </c>
       <c r="BJ60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="BK60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="BL60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="BM60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="BN60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="BO60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="BP60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="BQ60" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BR60" t="inlineStr">
@@ -22439,12 +22439,12 @@
       </c>
       <c r="BT60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BU60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
@@ -22481,7 +22481,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>4.59</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -22501,12 +22501,12 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.08</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
@@ -22606,12 +22606,12 @@
       </c>
       <c r="AF61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AG61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238</t>
         </is>
       </c>
       <c r="AH61" t="inlineStr">
@@ -22736,62 +22736,62 @@
       </c>
       <c r="BF61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-4.312824007547442</t>
         </is>
       </c>
       <c r="BG61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.60101708031618</t>
         </is>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-22.72990160044902</t>
         </is>
       </c>
       <c r="BI61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="BJ61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.04</t>
         </is>
       </c>
       <c r="BK61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7.59</t>
         </is>
       </c>
       <c r="BL61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>18.06</t>
         </is>
       </c>
       <c r="BM61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8.32%</t>
         </is>
       </c>
       <c r="BN61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.03%</t>
         </is>
       </c>
       <c r="BO61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14.36</t>
         </is>
       </c>
       <c r="BP61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="BQ61" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水龍頭零配件55.64%、水龍頭組裝件35.71%、其他8.64% (2024年)</t>
         </is>
       </c>
       <c r="BR61" t="inlineStr">
@@ -22806,12 +22806,12 @@
       </c>
       <c r="BT61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35.8</t>
         </is>
       </c>
       <c r="BU61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 其他 - 其他</t>
         </is>
       </c>
     </row>
@@ -26518,7 +26518,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -26538,7 +26538,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -26588,7 +26588,7 @@
       </c>
       <c r="U72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="V72" t="inlineStr">
@@ -26598,109 +26598,109 @@
       </c>
       <c r="W72" t="inlineStr">
         <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="X72" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>33.45</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD72" t="inlineStr">
+        <is>
+          <t>23.75</t>
+        </is>
+      </c>
+      <c r="AE72" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="AF72" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="AG72" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="AH72" t="inlineStr">
+        <is>
+          <t>-1.36</t>
+        </is>
+      </c>
+      <c r="AI72" t="inlineStr">
+        <is>
+          <t>-1.71</t>
+        </is>
+      </c>
+      <c r="AJ72" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="AK72" t="inlineStr">
+        <is>
+          <t>22.86</t>
+        </is>
+      </c>
+      <c r="AL72" t="inlineStr">
+        <is>
+          <t>23.2575</t>
+        </is>
+      </c>
+      <c r="AM72" t="inlineStr">
+        <is>
+          <t>23.057</t>
+        </is>
+      </c>
+      <c r="AN72" t="inlineStr">
+        <is>
+          <t>-128.48</t>
+        </is>
+      </c>
+      <c r="AO72" t="inlineStr">
+        <is>
+          <t>-0.13</t>
+        </is>
+      </c>
+      <c r="AP72" t="inlineStr">
+        <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AQ72" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X72" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y72" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="AA72" t="inlineStr">
-        <is>
-          <t>33.45</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD72" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="AE72" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="AF72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG72" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH72" t="inlineStr">
-        <is>
-          <t>-1.36</t>
-        </is>
-      </c>
-      <c r="AI72" t="inlineStr">
-        <is>
-          <t>-1.71</t>
-        </is>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>22.86</t>
-        </is>
-      </c>
-      <c r="AL72" t="inlineStr">
-        <is>
-          <t>23.2575</t>
-        </is>
-      </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>23.057</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>-128.48</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>-0.13</t>
-        </is>
-      </c>
-      <c r="AP72" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
-      <c r="AQ72" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AR72" t="inlineStr">
         <is>
           <t>3.703703703703719</t>
@@ -26768,67 +26768,67 @@
       </c>
       <c r="BE72" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="BJ72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ72" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR72" t="inlineStr">
@@ -26843,12 +26843,12 @@
       </c>
       <c r="BT72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -26885,7 +26885,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>10.25</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -26905,7 +26905,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -26955,7 +26955,7 @@
       </c>
       <c r="U73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28</t>
         </is>
       </c>
       <c r="V73" t="inlineStr">
@@ -26965,109 +26965,109 @@
       </c>
       <c r="W73" t="inlineStr">
         <is>
+          <t>2.0</t>
+        </is>
+      </c>
+      <c r="X73" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>33.45</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD73" t="inlineStr">
+        <is>
+          <t>23.75</t>
+        </is>
+      </c>
+      <c r="AE73" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="AF73" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="AG73" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="AH73" t="inlineStr">
+        <is>
+          <t>-0.57</t>
+        </is>
+      </c>
+      <c r="AI73" t="inlineStr">
+        <is>
+          <t>-1.70</t>
+        </is>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>22.93</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>23.3275</t>
+        </is>
+      </c>
+      <c r="AM73" t="inlineStr">
+        <is>
+          <t>23.082</t>
+        </is>
+      </c>
+      <c r="AN73" t="inlineStr">
+        <is>
+          <t>-146.09</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>-0.09</t>
+        </is>
+      </c>
+      <c r="AP73" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AQ73" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X73" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y73" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="AA73" t="inlineStr">
-        <is>
-          <t>33.45</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD73" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="AE73" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="AF73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG73" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH73" t="inlineStr">
-        <is>
-          <t>-0.57</t>
-        </is>
-      </c>
-      <c r="AI73" t="inlineStr">
-        <is>
-          <t>-1.70</t>
-        </is>
-      </c>
-      <c r="AJ73" t="inlineStr">
-        <is>
-          <t>1.06</t>
-        </is>
-      </c>
-      <c r="AK73" t="inlineStr">
-        <is>
-          <t>22.93</t>
-        </is>
-      </c>
-      <c r="AL73" t="inlineStr">
-        <is>
-          <t>23.3275</t>
-        </is>
-      </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>23.082</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>-146.09</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>-0.09</t>
-        </is>
-      </c>
-      <c r="AP73" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AQ73" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AR73" t="inlineStr">
         <is>
           <t>14.81481481481492</t>
@@ -27140,62 +27140,62 @@
       </c>
       <c r="BF73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BJ73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ73" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR73" t="inlineStr">
@@ -27210,12 +27210,12 @@
       </c>
       <c r="BT73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -27252,7 +27252,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>11.29</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -27272,7 +27272,7 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
@@ -27322,7 +27322,7 @@
       </c>
       <c r="U74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26</t>
         </is>
       </c>
       <c r="V74" t="inlineStr">
@@ -27332,7 +27332,7 @@
       </c>
       <c r="W74" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-1.0</t>
         </is>
       </c>
       <c r="X74" t="inlineStr">
@@ -27377,12 +27377,12 @@
       </c>
       <c r="AF74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH74" t="inlineStr">
@@ -27507,62 +27507,62 @@
       </c>
       <c r="BF74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BJ74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ74" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR74" t="inlineStr">
@@ -27577,12 +27577,12 @@
       </c>
       <c r="BT74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -27619,7 +27619,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>6.48</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -27639,7 +27639,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.22</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -27689,7 +27689,7 @@
       </c>
       <c r="U75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>27</t>
         </is>
       </c>
       <c r="V75" t="inlineStr">
@@ -27699,7 +27699,7 @@
       </c>
       <c r="W75" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-6.0</t>
         </is>
       </c>
       <c r="X75" t="inlineStr">
@@ -27744,12 +27744,12 @@
       </c>
       <c r="AF75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH75" t="inlineStr">
@@ -27874,62 +27874,62 @@
       </c>
       <c r="BF75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BJ75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ75" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR75" t="inlineStr">
@@ -27944,12 +27944,12 @@
       </c>
       <c r="BT75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -27986,7 +27986,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>8.43</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -28006,7 +28006,7 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -28056,7 +28056,7 @@
       </c>
       <c r="U76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>33</t>
         </is>
       </c>
       <c r="V76" t="inlineStr">
@@ -28066,7 +28066,7 @@
       </c>
       <c r="W76" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-9.0</t>
         </is>
       </c>
       <c r="X76" t="inlineStr">
@@ -28111,12 +28111,12 @@
       </c>
       <c r="AF76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH76" t="inlineStr">
@@ -28241,62 +28241,62 @@
       </c>
       <c r="BF76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BJ76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ76" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR76" t="inlineStr">
@@ -28311,12 +28311,12 @@
       </c>
       <c r="BT76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -28353,7 +28353,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>12.89</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -28373,7 +28373,7 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.55</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -28423,7 +28423,7 @@
       </c>
       <c r="U77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>42</t>
         </is>
       </c>
       <c r="V77" t="inlineStr">
@@ -28433,109 +28433,109 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="X77" t="inlineStr">
+        <is>
+          <t>2025-03-11 00:00:00</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-02-18 00:00:00</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>34.8</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>33.45</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>2025-10-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>2025-10-13 00:00:00</t>
+        </is>
+      </c>
+      <c r="AD77" t="inlineStr">
+        <is>
+          <t>23.75</t>
+        </is>
+      </c>
+      <c r="AE77" t="inlineStr">
+        <is>
+          <t>23.0</t>
+        </is>
+      </c>
+      <c r="AF77" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="AG77" t="inlineStr">
+        <is>
+          <t>22251</t>
+        </is>
+      </c>
+      <c r="AH77" t="inlineStr">
+        <is>
+          <t>-0.82</t>
+        </is>
+      </c>
+      <c r="AI77" t="inlineStr">
+        <is>
+          <t>-1.73</t>
+        </is>
+      </c>
+      <c r="AJ77" t="inlineStr">
+        <is>
+          <t>1.21</t>
+        </is>
+      </c>
+      <c r="AK77" t="inlineStr">
+        <is>
+          <t>23.09</t>
+        </is>
+      </c>
+      <c r="AL77" t="inlineStr">
+        <is>
+          <t>23.4975</t>
+        </is>
+      </c>
+      <c r="AM77" t="inlineStr">
+        <is>
+          <t>23.216</t>
+        </is>
+      </c>
+      <c r="AN77" t="inlineStr">
+        <is>
+          <t>-357.75</t>
+        </is>
+      </c>
+      <c r="AO77" t="inlineStr">
+        <is>
+          <t>-0.04</t>
+        </is>
+      </c>
+      <c r="AP77" t="inlineStr">
+        <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AQ77" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="X77" t="inlineStr">
-        <is>
-          <t>2025-03-11 00:00:00</t>
-        </is>
-      </c>
-      <c r="Y77" t="inlineStr">
-        <is>
-          <t>2025-02-18 00:00:00</t>
-        </is>
-      </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>34.8</t>
-        </is>
-      </c>
-      <c r="AA77" t="inlineStr">
-        <is>
-          <t>33.45</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>2025-10-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>2025-10-13 00:00:00</t>
-        </is>
-      </c>
-      <c r="AD77" t="inlineStr">
-        <is>
-          <t>23.75</t>
-        </is>
-      </c>
-      <c r="AE77" t="inlineStr">
-        <is>
-          <t>23.0</t>
-        </is>
-      </c>
-      <c r="AF77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AG77" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH77" t="inlineStr">
-        <is>
-          <t>-0.82</t>
-        </is>
-      </c>
-      <c r="AI77" t="inlineStr">
-        <is>
-          <t>-1.73</t>
-        </is>
-      </c>
-      <c r="AJ77" t="inlineStr">
-        <is>
-          <t>1.21</t>
-        </is>
-      </c>
-      <c r="AK77" t="inlineStr">
-        <is>
-          <t>23.09</t>
-        </is>
-      </c>
-      <c r="AL77" t="inlineStr">
-        <is>
-          <t>23.4975</t>
-        </is>
-      </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>23.216</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>-357.75</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>-0.04</t>
-        </is>
-      </c>
-      <c r="AP77" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AQ77" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AR77" t="inlineStr">
         <is>
           <t>35.41666666666675</t>
@@ -28603,67 +28603,67 @@
       </c>
       <c r="BE77" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="BJ77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ77" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR77" t="inlineStr">
@@ -28678,12 +28678,12 @@
       </c>
       <c r="BT77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -28720,7 +28720,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>11.74</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -28740,7 +28740,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.1</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -28790,7 +28790,7 @@
       </c>
       <c r="U78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>36</t>
         </is>
       </c>
       <c r="V78" t="inlineStr">
@@ -28800,7 +28800,7 @@
       </c>
       <c r="W78" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X78" t="inlineStr">
@@ -28845,12 +28845,12 @@
       </c>
       <c r="AF78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH78" t="inlineStr">
@@ -28975,62 +28975,62 @@
       </c>
       <c r="BF78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BJ78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ78" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR78" t="inlineStr">
@@ -29045,12 +29045,12 @@
       </c>
       <c r="BT78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -29087,7 +29087,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>17.58</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -29107,7 +29107,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-3.55</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -29157,7 +29157,7 @@
       </c>
       <c r="U79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34</t>
         </is>
       </c>
       <c r="V79" t="inlineStr">
@@ -29167,7 +29167,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>34.0</t>
         </is>
       </c>
       <c r="X79" t="inlineStr">
@@ -29212,12 +29212,12 @@
       </c>
       <c r="AF79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH79" t="inlineStr">
@@ -29337,67 +29337,67 @@
       </c>
       <c r="BE79" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BF79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="BJ79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR79" t="inlineStr">
@@ -29412,12 +29412,12 @@
       </c>
       <c r="BT79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU79" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -29454,7 +29454,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>7.04</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -29474,7 +29474,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-2.0</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -29579,12 +29579,12 @@
       </c>
       <c r="AF80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH80" t="inlineStr">
@@ -29709,62 +29709,62 @@
       </c>
       <c r="BF80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BJ80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ80" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR80" t="inlineStr">
@@ -29779,12 +29779,12 @@
       </c>
       <c r="BT80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU80" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>
@@ -29821,7 +29821,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>inf</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -29841,7 +29841,7 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.77</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -29946,12 +29946,12 @@
       </c>
       <c r="AF81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AG81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22251</t>
         </is>
       </c>
       <c r="AH81" t="inlineStr">
@@ -30076,62 +30076,62 @@
       </c>
       <c r="BF81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-9.760342271298851</t>
         </is>
       </c>
       <c r="BG81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-6.072228435914363</t>
         </is>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.189538872550337</t>
         </is>
       </c>
       <c r="BI81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="BJ81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.43</t>
         </is>
       </c>
       <c r="BK81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4.57</t>
         </is>
       </c>
       <c r="BL81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21.89</t>
         </is>
       </c>
       <c r="BM81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15.12%</t>
         </is>
       </c>
       <c r="BN81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3.15%</t>
         </is>
       </c>
       <c r="BO81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30.23</t>
         </is>
       </c>
       <c r="BP81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>170279</t>
         </is>
       </c>
       <c r="BQ81" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>水泥,預拌混擬土76.31%、電力供給及儲能,可充式鋰離20.52%、海陸運輸3.17% (2024年)</t>
         </is>
       </c>
       <c r="BR81" t="inlineStr">
@@ -30146,12 +30146,12 @@
       </c>
       <c r="BT81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>28.5</t>
         </is>
       </c>
       <c r="BU81" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>** 水泥 - 石灰石、水泥生料、水泥熟料、水泥成品、預拌混凝土</t>
         </is>
       </c>
     </row>

--- a/Result/checksunmy.xlsx
+++ b/Result/checksunmy.xlsx
@@ -1011,15 +1011,11 @@
           <t>222.15</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>237.48</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>233.225</t>
-        </is>
+      <c r="AN2" t="n">
+        <v>237.48</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>233.225</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -1398,15 +1394,11 @@
           <t>223.575</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>238.39</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>233.39375</t>
-        </is>
+      <c r="AN3" t="n">
+        <v>238.39</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>233.39375</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1785,15 +1777,11 @@
           <t>224.775</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>239.35</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>233.6625</t>
-        </is>
+      <c r="AN4" t="n">
+        <v>239.35</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>233.6625</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -2172,15 +2160,11 @@
           <t>226.225</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>240.47</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>233.89375</t>
-        </is>
+      <c r="AN5" t="n">
+        <v>240.47</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>233.89375</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -2559,15 +2543,11 @@
           <t>227.95</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>241.59</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>234.0625</t>
-        </is>
+      <c r="AN6" t="n">
+        <v>241.59</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>234.0625</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -2946,15 +2926,11 @@
           <t>229.475</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>242.66</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>234.18125</t>
-        </is>
+      <c r="AN7" t="n">
+        <v>242.66</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>234.18125</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -3333,15 +3309,11 @@
           <t>230.35</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>243.39</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>234.2</t>
-        </is>
+      <c r="AN8" t="n">
+        <v>243.39</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>234.2</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -3720,15 +3692,11 @@
           <t>231.4</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>243.85</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>234.2875</t>
-        </is>
+      <c r="AN9" t="n">
+        <v>243.85</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>234.2875</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -4107,15 +4075,11 @@
           <t>232.3</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>244.15</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>234.31875</t>
-        </is>
+      <c r="AN10" t="n">
+        <v>244.15</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>234.31875</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -4494,15 +4458,11 @@
           <t>233.2</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>244.1</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>234.29375</t>
-        </is>
+      <c r="AN11" t="n">
+        <v>244.1</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>234.29375</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -4881,15 +4841,11 @@
           <t>42.5875</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>42.68</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>42.16187499999999</t>
-        </is>
+      <c r="AN12" t="n">
+        <v>42.68</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>42.16187499999999</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -5268,15 +5224,11 @@
           <t>42.67</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>42.747</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>42.1425</t>
-        </is>
+      <c r="AN13" t="n">
+        <v>42.747</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>42.1425</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -5655,15 +5607,11 @@
           <t>42.71</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>42.835</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>42.12625</t>
-        </is>
+      <c r="AN14" t="n">
+        <v>42.835</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>42.12625</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -6042,15 +5990,11 @@
           <t>42.77249999999999</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>42.825</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>42.11062500000001</t>
-        </is>
+      <c r="AN15" t="n">
+        <v>42.825</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>42.11062500000001</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -6429,15 +6373,11 @@
           <t>42.8825</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>42.813</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>42.0975</t>
-        </is>
+      <c r="AN16" t="n">
+        <v>42.813</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>42.0975</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -6816,15 +6756,11 @@
           <t>42.9275</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>42.809</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>42.07875</t>
-        </is>
+      <c r="AN17" t="n">
+        <v>42.809</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>42.07875</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -7203,15 +7139,11 @@
           <t>42.9425</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>42.78299999999999</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>42.0575</t>
-        </is>
+      <c r="AN18" t="n">
+        <v>42.78299999999999</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>42.0575</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -7590,15 +7522,11 @@
           <t>42.92</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>42.754</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>42.038125</t>
-        </is>
+      <c r="AN19" t="n">
+        <v>42.754</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>42.038125</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -7977,15 +7905,11 @@
           <t>42.9175</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>42.71900000000001</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>42.021875</t>
-        </is>
+      <c r="AN20" t="n">
+        <v>42.71900000000001</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>42.021875</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -8364,15 +8288,11 @@
           <t>42.9</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>42.709</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>42.008125</t>
-        </is>
+      <c r="AN21" t="n">
+        <v>42.709</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>42.008125</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -8751,15 +8671,11 @@
           <t>369.25</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>374.19</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>364.30625</t>
-        </is>
+      <c r="AN22" t="n">
+        <v>374.19</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>364.30625</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -9138,15 +9054,11 @@
           <t>371.15</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>374.12</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>364.04375</t>
-        </is>
+      <c r="AN23" t="n">
+        <v>374.12</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>364.04375</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -9525,15 +9437,11 @@
           <t>372.475</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>374.14</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>363.9125</t>
-        </is>
+      <c r="AN24" t="n">
+        <v>374.14</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>363.9125</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -9912,15 +9820,11 @@
           <t>375.1</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>374.11</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>363.8375</t>
-        </is>
+      <c r="AN25" t="n">
+        <v>374.11</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>363.8375</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -10299,15 +10203,11 @@
           <t>378.85</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>374.14</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>363.8125</t>
-        </is>
+      <c r="AN26" t="n">
+        <v>374.14</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>363.8125</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -10686,15 +10586,11 @@
           <t>380.35</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>374.19</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>363.71875</t>
-        </is>
+      <c r="AN27" t="n">
+        <v>374.19</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>363.71875</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -11073,15 +10969,11 @@
           <t>381.2</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>374.3</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>363.5625</t>
-        </is>
+      <c r="AN28" t="n">
+        <v>374.3</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>363.5625</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -11460,15 +11352,11 @@
           <t>381.55</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>374.51</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>363.5</t>
-        </is>
+      <c r="AN29" t="n">
+        <v>374.51</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>363.5</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -11847,15 +11735,11 @@
           <t>381.9</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>374.64</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>363.34375</t>
-        </is>
+      <c r="AN30" t="n">
+        <v>374.64</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>363.34375</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -12234,15 +12118,11 @@
           <t>381.25</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>374.02</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>363.2125</t>
-        </is>
+      <c r="AN31" t="n">
+        <v>374.02</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>363.2125</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -12621,15 +12501,11 @@
           <t>14.4725</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>15.519</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>15.411875</t>
-        </is>
+      <c r="AN32" t="n">
+        <v>15.519</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>15.411875</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -13008,15 +12884,11 @@
           <t>14.5175</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>15.592</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>15.42125</t>
-        </is>
+      <c r="AN33" t="n">
+        <v>15.592</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>15.42125</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -13395,15 +13267,11 @@
           <t>14.56</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>15.671</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>15.425625</t>
-        </is>
+      <c r="AN34" t="n">
+        <v>15.671</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>15.425625</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -13782,15 +13650,11 @@
           <t>14.6125</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>15.755</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>15.43375</t>
-        </is>
+      <c r="AN35" t="n">
+        <v>15.755</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>15.43375</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -14169,15 +14033,11 @@
           <t>14.6725</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>15.84</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>15.44625</t>
-        </is>
+      <c r="AN36" t="n">
+        <v>15.84</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>15.44625</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -14556,15 +14416,11 @@
           <t>14.7375</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>15.915</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>15.458125</t>
-        </is>
+      <c r="AN37" t="n">
+        <v>15.915</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>15.458125</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -14943,15 +14799,11 @@
           <t>14.8</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>15.954</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>15.4675</t>
-        </is>
+      <c r="AN38" t="n">
+        <v>15.954</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>15.4675</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -15330,15 +15182,11 @@
           <t>14.865</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>15.993</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>15.47875</t>
-        </is>
+      <c r="AN39" t="n">
+        <v>15.993</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>15.47875</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -15717,15 +15565,11 @@
           <t>14.945</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>16.056</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>15.494375</t>
-        </is>
+      <c r="AN40" t="n">
+        <v>16.056</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>15.494375</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -16104,15 +15948,11 @@
           <t>15.0125</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>16.088</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>15.51</t>
-        </is>
+      <c r="AN41" t="n">
+        <v>16.088</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>15.51</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -16491,15 +16331,11 @@
           <t>39.0325</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>41.663</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>41.701875</t>
-        </is>
+      <c r="AN42" t="n">
+        <v>41.663</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>41.701875</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -16878,15 +16714,11 @@
           <t>39.095</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>41.73699999999999</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>41.73375</t>
-        </is>
+      <c r="AN43" t="n">
+        <v>41.73699999999999</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>41.73375</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -17265,15 +17097,11 @@
           <t>39.2</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>41.8</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>41.765625</t>
-        </is>
+      <c r="AN44" t="n">
+        <v>41.8</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>41.765625</v>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
@@ -17652,15 +17480,11 @@
           <t>39.2975</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>41.861</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>41.80562500000001</t>
-        </is>
+      <c r="AN45" t="n">
+        <v>41.861</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>41.80562500000001</v>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
@@ -18039,15 +17863,11 @@
           <t>39.5875</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>41.917</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>41.844375</t>
-        </is>
+      <c r="AN46" t="n">
+        <v>41.917</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>41.844375</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
@@ -18426,15 +18246,11 @@
           <t>39.87</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>41.977</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>41.879375</t>
-        </is>
+      <c r="AN47" t="n">
+        <v>41.977</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>41.879375</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
@@ -18813,15 +18629,11 @@
           <t>40.18</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>42.043</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>41.911875</t>
-        </is>
+      <c r="AN48" t="n">
+        <v>42.043</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>41.911875</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
@@ -19200,15 +19012,11 @@
           <t>40.475</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>42.11</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>41.94312499999999</t>
-        </is>
+      <c r="AN49" t="n">
+        <v>42.11</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>41.94312499999999</v>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
@@ -19587,15 +19395,11 @@
           <t>40.86</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>42.17899999999999</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>41.986875</t>
-        </is>
+      <c r="AN50" t="n">
+        <v>42.17899999999999</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>41.986875</v>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
@@ -19974,15 +19778,11 @@
           <t>41.285</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>42.258</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>42.0275</t>
-        </is>
+      <c r="AN51" t="n">
+        <v>42.258</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>42.0275</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
@@ -20361,15 +20161,11 @@
           <t>22.09</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>22.656</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>23.406875</t>
-        </is>
+      <c r="AN52" t="n">
+        <v>22.656</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>23.406875</v>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
@@ -20748,15 +20544,11 @@
           <t>22.0975</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>22.727</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>23.4475</t>
-        </is>
+      <c r="AN53" t="n">
+        <v>22.727</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>23.4475</v>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
@@ -21135,15 +20927,11 @@
           <t>22.0825</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>22.797</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>23.486875</t>
-        </is>
+      <c r="AN54" t="n">
+        <v>22.797</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>23.486875</v>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
@@ -21522,15 +21310,11 @@
           <t>22.08</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>22.85</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>23.523125</t>
-        </is>
+      <c r="AN55" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>23.523125</v>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
@@ -21909,15 +21693,11 @@
           <t>22.07</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>22.898</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>23.551875</t>
-        </is>
+      <c r="AN56" t="n">
+        <v>22.898</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>23.551875</v>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
@@ -22296,15 +22076,11 @@
           <t>22.0575</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>22.94</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>23.576875</t>
-        </is>
+      <c r="AN57" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>23.576875</v>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
@@ -22683,15 +22459,11 @@
           <t>22.02</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>22.98</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>23.594375</t>
-        </is>
+      <c r="AN58" t="n">
+        <v>22.98</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>23.594375</v>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
@@ -23070,15 +22842,11 @@
           <t>21.97</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>23.02</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>23.61125</t>
-        </is>
+      <c r="AN59" t="n">
+        <v>23.02</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>23.61125</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
@@ -23457,15 +23225,11 @@
           <t>21.955</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>23.064</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>23.629375</t>
-        </is>
+      <c r="AN60" t="n">
+        <v>23.064</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>23.629375</v>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
@@ -23844,15 +23608,11 @@
           <t>21.945</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>23.114</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>23.653125</t>
-        </is>
+      <c r="AN61" t="n">
+        <v>23.114</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>23.653125</v>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
@@ -24231,15 +23991,11 @@
           <t>28.62</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>30.017</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>30.869375</t>
-        </is>
+      <c r="AN62" t="n">
+        <v>30.017</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>30.869375</v>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
@@ -24618,15 +24374,11 @@
           <t>28.63</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>30.083</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>30.878125</t>
-        </is>
+      <c r="AN63" t="n">
+        <v>30.083</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>30.878125</v>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
@@ -25005,15 +24757,11 @@
           <t>28.6625</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>30.143</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>30.895625</t>
-        </is>
+      <c r="AN64" t="n">
+        <v>30.143</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>30.895625</v>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
@@ -25392,15 +25140,11 @@
           <t>28.6975</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>30.21</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>30.903125</t>
-        </is>
+      <c r="AN65" t="n">
+        <v>30.21</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>30.903125</v>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
@@ -25779,15 +25523,11 @@
           <t>28.7575</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>30.277</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>30.9125</t>
-        </is>
+      <c r="AN66" t="n">
+        <v>30.277</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>30.9125</v>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
@@ -26166,15 +25906,11 @@
           <t>28.8</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>30.351</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>30.9225</t>
-        </is>
+      <c r="AN67" t="n">
+        <v>30.351</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>30.9225</v>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
@@ -26553,15 +26289,11 @@
           <t>28.865</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>30.419</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>30.935</t>
-        </is>
+      <c r="AN68" t="n">
+        <v>30.419</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>30.935</v>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
@@ -26940,15 +26672,11 @@
           <t>28.9375</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>30.505</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>30.951875</t>
-        </is>
+      <c r="AN69" t="n">
+        <v>30.505</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>30.951875</v>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
@@ -27327,15 +27055,11 @@
           <t>29.02</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>30.587</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>30.965625</t>
-        </is>
+      <c r="AN70" t="n">
+        <v>30.587</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>30.965625</v>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
@@ -27714,15 +27438,11 @@
           <t>29.03</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>30.655</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>30.95875</t>
-        </is>
+      <c r="AN71" t="n">
+        <v>30.655</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>30.95875</v>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
@@ -28101,15 +27821,11 @@
           <t>23.0875</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>22.993</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>23.395625</t>
-        </is>
+      <c r="AN72" t="n">
+        <v>22.993</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>23.395625</v>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
@@ -28488,15 +28204,11 @@
           <t>23.1825</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>23.029</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>23.43</t>
-        </is>
+      <c r="AN73" t="n">
+        <v>23.029</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>23.43</v>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
@@ -28875,15 +28587,11 @@
           <t>23.2575</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>23.057</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>23.46375</t>
-        </is>
+      <c r="AN74" t="n">
+        <v>23.057</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>23.46375</v>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
@@ -29262,15 +28970,11 @@
           <t>23.3275</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>23.082</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>23.49875</t>
-        </is>
+      <c r="AN75" t="n">
+        <v>23.082</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>23.49875</v>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
@@ -29649,15 +29353,11 @@
           <t>23.36</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>23.121</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>23.529375</t>
-        </is>
+      <c r="AN76" t="n">
+        <v>23.121</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>23.529375</v>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
@@ -30036,15 +29736,11 @@
           <t>23.4</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>23.157</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>23.569375</t>
-        </is>
+      <c r="AN77" t="n">
+        <v>23.157</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>23.569375</v>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
@@ -30423,15 +30119,11 @@
           <t>23.4775</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>23.188</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>23.6</t>
-        </is>
+      <c r="AN78" t="n">
+        <v>23.188</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>23.6</v>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
@@ -30810,15 +30502,11 @@
           <t>23.4975</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>23.216</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>23.640625</t>
-        </is>
+      <c r="AN79" t="n">
+        <v>23.216</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>23.640625</v>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
@@ -31197,15 +30885,11 @@
           <t>23.4625</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>23.244</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>23.676875</t>
-        </is>
+      <c r="AN80" t="n">
+        <v>23.244</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>23.676875</v>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
@@ -31584,15 +31268,11 @@
           <t>23.41</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>23.26600000000001</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>23.7075</t>
-        </is>
+      <c r="AN81" t="n">
+        <v>23.26600000000001</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>23.7075</v>
       </c>
       <c r="AP81" t="inlineStr">
         <is>

--- a/Result/checksunmy.xlsx
+++ b/Result/checksunmy.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d1】;【d2】;【x】看好</t>
+          <t>【d1】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1300,7 +1300,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1727,7 +1727,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2154,7 +2154,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2581,7 +2581,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3008,7 +3008,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3435,7 +3435,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3862,7 +3862,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4287,7 +4287,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>8069</t>
@@ -4710,7 +4714,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>8069</t>
@@ -5133,7 +5141,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>8069</t>
@@ -5556,7 +5568,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>3594</t>
@@ -5978,7 +5994,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>3594</t>
@@ -6400,7 +6420,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>3594</t>
@@ -6822,7 +6846,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>3594</t>
@@ -7244,7 +7272,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>3594</t>
@@ -7666,7 +7698,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>3594</t>
@@ -10218,7 +10254,11 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr"/>
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B24" t="inlineStr">
         <is>
           <t>3583</t>
@@ -10643,7 +10683,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>3583</t>
@@ -11068,7 +11112,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>3583</t>
@@ -11493,7 +11541,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>3583</t>
@@ -11918,7 +11970,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>3583</t>
@@ -12343,7 +12399,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>3583</t>
@@ -12768,7 +12828,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>3583</t>
@@ -13193,7 +13257,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>3583</t>
@@ -14907,7 +14975,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15334,7 +15402,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15761,7 +15829,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16188,7 +16256,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16613,7 +16681,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>3066</t>
@@ -19600,7 +19672,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20026,7 +20098,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20452,7 +20524,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -20878,7 +20950,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21302,7 +21374,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2542</t>
@@ -21724,7 +21800,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2542</t>
@@ -22146,7 +22226,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2542</t>
@@ -22568,7 +22652,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2542</t>
@@ -22990,7 +23078,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2542</t>
@@ -24266,7 +24358,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -24692,7 +24784,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25118,7 +25210,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25544,7 +25636,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -25970,7 +26062,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26394,7 +26486,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>2062</t>
@@ -26816,7 +26912,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>2062</t>
@@ -27238,7 +27338,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>2062</t>
@@ -28938,7 +29042,11 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" t="inlineStr"/>
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B68" t="inlineStr">
         <is>
           <t>1599</t>
@@ -29361,7 +29469,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>1599</t>
@@ -30638,7 +30750,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>1599</t>
@@ -31061,7 +31177,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>1599</t>
@@ -31484,7 +31604,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>1599</t>
@@ -31907,7 +32031,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>1599</t>
@@ -32330,7 +32458,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>1599</t>
@@ -33180,7 +33312,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>1599</t>
@@ -34030,7 +34166,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>1229</t>
@@ -34453,7 +34593,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>1229</t>
@@ -34878,7 +35022,7 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -35303,7 +35447,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>1229</t>
@@ -35728,7 +35876,7 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -36153,7 +36301,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>1229</t>
@@ -36576,7 +36728,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>1229</t>
@@ -38282,7 +38438,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -38712,7 +38868,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -39142,7 +39298,7 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -39572,7 +39728,7 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -40002,7 +40158,7 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -40432,7 +40588,7 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>【d1】;【d2】</t>
+          <t>【d1】</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -40860,7 +41016,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>1101</t>
@@ -41286,7 +41446,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>【d2】</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>1101</t>
